--- a/restore-pictures/src/test/resources/family_blog_ngg_gallery.xlsx
+++ b/restore-pictures/src/test/resources/family_blog_ngg_gallery.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Windows_folders\Downloads\setup\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\workspace\java\restore-pictures\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{779A57FE-6146-48DF-9F74-01C6278EFC76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA860622-AE52-424E-A214-A2CAEC6C1A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{65F6A760-9BB8-43D4-8DE2-62713A59A0D9}"/>
   </bookViews>
@@ -6661,592 +6661,592 @@
     <t>OneDrivePath</t>
   </si>
   <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-02_Lyon</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-03_train</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-04_Lego_chinois</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-05_seance_photos</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-07_fin_conges_noel</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-12</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-13</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-14</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-15</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-16</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-17</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-18</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-19</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-20</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-21</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-22</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-23</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-24</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-25</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-26</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-27</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-28</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-14_Lego</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-29</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-30</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-31</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-32</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-33</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-34</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-35</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-36</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-27_dragon_dance</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-02</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-03</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-04</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-05</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-06</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-07</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-08</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-09</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-10</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-11</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-12</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-13</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-14</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-15</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-16</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-17</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-18</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-19</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-20</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-21</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-22</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-23</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-24</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-25</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-15_maison</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-17_Spectacle_chinois</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-17_Yu</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-24_Chinese_culture</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-29_moisniversaire</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-02_Metz</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-03_Verdun</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-08_maison</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-09_Aachen</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-10_Cavalcade_petange</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-28_Luxembourg</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-30_Dusseldorf</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-31_Koln</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-31_Wuppertal</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-01_Bonn</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-01_Drachenburg</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-05_depart_waigong</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-06_Mainz</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-06_Wiesbaden</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-10_Cargo_Lilian</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-13_Velo_differdange</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-23_at_home</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-27_Mamer</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-28_Deierpark</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-01</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-02</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-03</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-04</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-05</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-06</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-07</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-08</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-09</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-10</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-11</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-12</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-13</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-14</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-15</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-16</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-17</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-18</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-19</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-20</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-21</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-22</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-23</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-24</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-05_Velodukt</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-10_fete_kannercampus</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-11_Esch_Alzette</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-12_Jaulny</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-13_at_home</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-19_concert_chine</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-20_Wiltz</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\Barcelone\Parc_Guell</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\Barcelone\Rambla</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\Barcelone\Parc_Montjuic</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-26_Cannes</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\bateau_MSC</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-26_Nice</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-27_Genes</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-28_Cinque_Terre\2.Manarola</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-28_Cinque_Terre\3.Monterosso</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-28_Cinque_Terre\1.Riomaggiore</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-29_Tarquina</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-29_Tuscania</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-31_Palma_Majorca</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-31_Palma_Majorca\cathédrale</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\Barcelone\Sagrada_Familia</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Voyages\2024-06_croisiere\Barcelone\old_city</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-06-10_Alexis_programmation</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-06-17_Ceratizit</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-06-23_fete_nationale</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-06-29_1_an_Lilian</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-17</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-18</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-19</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-20</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-21</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-22</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-23</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-24</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-25</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-26</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-27</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\2024-07-27_arrivee</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\00_Alexis_WaiPo_WaiGong</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\ecoles</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\centre_ville</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\petite_france</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\centre_historique</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\Nanqiang</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\shopping</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\temple_exterieur</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\montagne_ouest</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\Parc_daguanlou</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\Rongchuang</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\lac_vert</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\maison_gouverneur_Kunming</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\Maison_Zhou_De</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\marche</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\temple_lac_vert</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\Jinning\restaurant</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\Jinning</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\maison_maire_Kunming</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\observatoire</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\village_100_herbes\temple</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\village_100_herbes</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\HaiYan</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\Jinning\musee_Dian</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\Jinning\parc_Zheng_He</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\Train</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\03_Shanghai</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\03_Shanghai\Nanjing_road</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\03_Shanghai\XinTianDi</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\03_Shanghai\The_bund</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\03_Shanghai\Concession_francaise</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\04_Hangzhou\Lac_ouest</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\03_Shanghai\Nanjing_road\lego</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\03_Shanghai\Yuyuan_garden</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\04_Hangzhou\temple_bouddhiste</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\04_Hangzhou\Confucius</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\04_Hangzhou\Leifeng_pagoda</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\04_Hangzhou</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\05_Xiamen\CB_CT</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\05_Xiamen\Botanical_garden</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\05_Xiamen\pearl_beach</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\05_Xiamen\Shimao_towers</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\05_Xiamen</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\05_Xiamen\Gulangyu_island</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\05_Xiamen\Siming_district</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\06_Quanzhou\Amie_xiongmette</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\06_Quanzhou\vieille_ville</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\06_Quanzhou\Kaiyuan_bouddhist_temple</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\06_Quanzhou\GuanDi_temple</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\06_Quanzhou</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\06_Quanzhou\Qingjing_mosque</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\06_Quanzhou\Tao</t>
-  </si>
-  <si>
-    <t>E:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\marche_fleurs</t>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-02_Lyon</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-03_train</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-04_Lego_chinois</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-05_seance_photos</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-07_fin_conges_noel</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-12</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-13</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-14</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-15</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-16</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-17</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-18</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-19</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-20</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-21</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-22</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-23</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-24</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-25</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-26</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-27</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-28</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-14_Lego</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-29</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-30</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-31</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-32</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-33</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-34</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-35</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-36</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-01-27_dragon_dance</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-02</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-03</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-04</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-05</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-06</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-07</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-08</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-09</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-10</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-11</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-12</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-13</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-14</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-15</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-16</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-17</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-18</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-19</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-20</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-21</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-22</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-23</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-24</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-25</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-15_maison</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-17_Spectacle_chinois</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-17_Yu</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-24_Chinese_culture</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-02-29_moisniversaire</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-02_Metz</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-03_Verdun</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-08_maison</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-09_Aachen</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-10_Cavalcade_petange</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-28_Luxembourg</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-30_Dusseldorf</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-31_Koln</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-03-31_Wuppertal</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-01_Bonn</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-01_Drachenburg</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-05_depart_waigong</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-06_Mainz</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-06_Wiesbaden</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-10_Cargo_Lilian</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-13_Velo_differdange</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-23_at_home</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-27_Mamer</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-04-28_Deierpark</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-01</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-02</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-03</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-04</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-05</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-06</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-07</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-08</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-09</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-10</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-11</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-12</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-13</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-14</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-15</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-16</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-17</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-18</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-19</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-20</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-21</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-22</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-23</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-24</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-05_Velodukt</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-10_fete_kannercampus</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-11_Esch_Alzette</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-12_Jaulny</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-13_at_home</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-19_concert_chine</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-05-20_Wiltz</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-06-10_Alexis_programmation</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-06-17_Ceratizit</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-06-23_fete_nationale</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-06-29_1_an_Lilian</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-17</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-18</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-19</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-20</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-21</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-22</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-23</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-24</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-25</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-26</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Xiongmaos_Famille\2024\2024-07-27</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\Barcelone\Parc_Guell</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\Barcelone\Rambla</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\Barcelone\Parc_Montjuic</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-26_Cannes</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\bateau_MSC</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-26_Nice</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-27_Genes</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-28_Cinque_Terre\2.Manarola</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-28_Cinque_Terre\3.Monterosso</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-28_Cinque_Terre\1.Riomaggiore</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-29_Tarquina</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-29_Tuscania</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-31_Palma_Majorca</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\2024-05-31_Palma_Majorca\cathédrale</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\Barcelone\Sagrada_Familia</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Photos\Voyages\2024-06_croisiere\Barcelone\old_city</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\2024-07-27_arrivee</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\00_Alexis_WaiPo_WaiGong</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\ecoles</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\centre_ville</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\petite_france</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\centre_historique</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\Nanqiang</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\shopping</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\temple_exterieur</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\montagne_ouest</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\Parc_daguanlou</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\Rongchuang</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\lac_vert</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\maison_gouverneur_Kunming</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\Maison_Zhou_De</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\marche</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\temple_lac_vert</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\Jinning\restaurant</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\Jinning</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\maison_maire_Kunming</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\observatoire</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\village_100_herbes\temple</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\village_100_herbes</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\HaiYan</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\Jinning\musee_Dian</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\Jinning\parc_Zheng_He</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\02_Lac_Dian\Train</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\03_Shanghai</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\03_Shanghai\Nanjing_road</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\03_Shanghai\XinTianDi</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\03_Shanghai\The_bund</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\03_Shanghai\Concession_francaise</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\04_Hangzhou\Lac_ouest</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\03_Shanghai\Nanjing_road\lego</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\03_Shanghai\Yuyuan_garden</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\04_Hangzhou\temple_bouddhiste</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\04_Hangzhou\Confucius</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\04_Hangzhou\Leifeng_pagoda</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\04_Hangzhou</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\05_Xiamen\CB_CT</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\05_Xiamen\Botanical_garden</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\05_Xiamen\pearl_beach</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\05_Xiamen\Shimao_towers</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\05_Xiamen</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\05_Xiamen\Gulangyu_island</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\05_Xiamen\Siming_district</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\06_Quanzhou\Amie_xiongmette</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\06_Quanzhou\vieille_ville</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\06_Quanzhou\Kaiyuan_bouddhist_temple</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\06_Quanzhou\GuanDi_temple</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\06_Quanzhou</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\06_Quanzhou\Qingjing_mosque</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\06_Quanzhou\Tao</t>
+  </si>
+  <si>
+    <t>G:\OneDrive\Pictures\Photos_a_trier\Chine2024\01_Kunming\marche_fleurs</t>
   </si>
 </sst>
 </file>
@@ -19986,7 +19986,7 @@
         <v>1432</v>
       </c>
       <c r="E698" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="699" spans="1:5" x14ac:dyDescent="0.3">
@@ -20003,7 +20003,7 @@
         <v>1431</v>
       </c>
       <c r="E699" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="700" spans="1:5" x14ac:dyDescent="0.3">
@@ -20020,7 +20020,7 @@
         <v>1430</v>
       </c>
       <c r="E700" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="701" spans="1:5" x14ac:dyDescent="0.3">
@@ -20037,7 +20037,7 @@
         <v>1429</v>
       </c>
       <c r="E701" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="702" spans="1:5" x14ac:dyDescent="0.3">
@@ -20054,7 +20054,7 @@
         <v>1428</v>
       </c>
       <c r="E702" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="703" spans="1:5" x14ac:dyDescent="0.3">
@@ -20071,7 +20071,7 @@
         <v>1427</v>
       </c>
       <c r="E703" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="704" spans="1:5" x14ac:dyDescent="0.3">
@@ -20088,7 +20088,7 @@
         <v>1426</v>
       </c>
       <c r="E704" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.3">
@@ -20105,7 +20105,7 @@
         <v>1423</v>
       </c>
       <c r="E705" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.3">
@@ -20122,7 +20122,7 @@
         <v>1422</v>
       </c>
       <c r="E706" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="707" spans="1:5" x14ac:dyDescent="0.3">
@@ -20139,7 +20139,7 @@
         <v>1421</v>
       </c>
       <c r="E707" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="708" spans="1:5" x14ac:dyDescent="0.3">
@@ -20156,7 +20156,7 @@
         <v>1420</v>
       </c>
       <c r="E708" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="709" spans="1:5" x14ac:dyDescent="0.3">
@@ -20173,7 +20173,7 @@
         <v>1419</v>
       </c>
       <c r="E709" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="710" spans="1:5" x14ac:dyDescent="0.3">
@@ -20190,7 +20190,7 @@
         <v>1418</v>
       </c>
       <c r="E710" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="711" spans="1:5" x14ac:dyDescent="0.3">
@@ -20207,7 +20207,7 @@
         <v>1417</v>
       </c>
       <c r="E711" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="712" spans="1:5" x14ac:dyDescent="0.3">
@@ -20224,7 +20224,7 @@
         <v>1416</v>
       </c>
       <c r="E712" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="713" spans="1:5" x14ac:dyDescent="0.3">
@@ -20241,7 +20241,7 @@
         <v>1415</v>
       </c>
       <c r="E713" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="714" spans="1:5" x14ac:dyDescent="0.3">
@@ -20258,7 +20258,7 @@
         <v>1414</v>
       </c>
       <c r="E714" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="715" spans="1:5" x14ac:dyDescent="0.3">
@@ -20275,7 +20275,7 @@
         <v>1413</v>
       </c>
       <c r="E715" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="716" spans="1:5" x14ac:dyDescent="0.3">
@@ -20292,7 +20292,7 @@
         <v>1412</v>
       </c>
       <c r="E716" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="717" spans="1:5" x14ac:dyDescent="0.3">
@@ -20309,7 +20309,7 @@
         <v>1411</v>
       </c>
       <c r="E717" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="718" spans="1:5" x14ac:dyDescent="0.3">
@@ -20326,7 +20326,7 @@
         <v>1410</v>
       </c>
       <c r="E718" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="719" spans="1:5" x14ac:dyDescent="0.3">
@@ -20343,7 +20343,7 @@
         <v>1407</v>
       </c>
       <c r="E719" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="720" spans="1:5" x14ac:dyDescent="0.3">
@@ -20360,7 +20360,7 @@
         <v>1406</v>
       </c>
       <c r="E720" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="721" spans="1:5" x14ac:dyDescent="0.3">
@@ -20377,7 +20377,7 @@
         <v>1405</v>
       </c>
       <c r="E721" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.3">
@@ -20394,7 +20394,7 @@
         <v>1404</v>
       </c>
       <c r="E722" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="723" spans="1:5" x14ac:dyDescent="0.3">
@@ -20411,7 +20411,7 @@
         <v>1403</v>
       </c>
       <c r="E723" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="724" spans="1:5" x14ac:dyDescent="0.3">
@@ -20428,7 +20428,7 @@
         <v>1402</v>
       </c>
       <c r="E724" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="725" spans="1:5" x14ac:dyDescent="0.3">
@@ -20445,7 +20445,7 @@
         <v>1401</v>
       </c>
       <c r="E725" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="726" spans="1:5" x14ac:dyDescent="0.3">
@@ -20462,7 +20462,7 @@
         <v>1400</v>
       </c>
       <c r="E726" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="727" spans="1:5" x14ac:dyDescent="0.3">
@@ -20479,7 +20479,7 @@
         <v>1399</v>
       </c>
       <c r="E727" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.3">
@@ -20496,7 +20496,7 @@
         <v>1398</v>
       </c>
       <c r="E728" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="729" spans="1:5" x14ac:dyDescent="0.3">
@@ -20513,7 +20513,7 @@
         <v>1397</v>
       </c>
       <c r="E729" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="730" spans="1:5" x14ac:dyDescent="0.3">
@@ -20530,7 +20530,7 @@
         <v>1396</v>
       </c>
       <c r="E730" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="731" spans="1:5" x14ac:dyDescent="0.3">
@@ -20547,7 +20547,7 @@
         <v>1395</v>
       </c>
       <c r="E731" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="732" spans="1:5" x14ac:dyDescent="0.3">
@@ -20564,7 +20564,7 @@
         <v>1394</v>
       </c>
       <c r="E732" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.3">
@@ -20581,7 +20581,7 @@
         <v>1393</v>
       </c>
       <c r="E733" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="734" spans="1:5" x14ac:dyDescent="0.3">
@@ -20598,7 +20598,7 @@
         <v>1392</v>
       </c>
       <c r="E734" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.3">
@@ -20615,7 +20615,7 @@
         <v>1391</v>
       </c>
       <c r="E735" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="736" spans="1:5" x14ac:dyDescent="0.3">
@@ -20632,7 +20632,7 @@
         <v>1390</v>
       </c>
       <c r="E736" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="737" spans="1:5" x14ac:dyDescent="0.3">
@@ -20649,7 +20649,7 @@
         <v>1389</v>
       </c>
       <c r="E737" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="738" spans="1:5" x14ac:dyDescent="0.3">
@@ -20666,7 +20666,7 @@
         <v>1388</v>
       </c>
       <c r="E738" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="739" spans="1:5" x14ac:dyDescent="0.3">
@@ -20683,7 +20683,7 @@
         <v>1385</v>
       </c>
       <c r="E739" t="s">
-        <v>2326</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="740" spans="1:5" x14ac:dyDescent="0.3">
@@ -20700,7 +20700,7 @@
         <v>1384</v>
       </c>
       <c r="E740" t="s">
-        <v>2326</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="741" spans="1:5" x14ac:dyDescent="0.3">
@@ -20717,7 +20717,7 @@
         <v>1383</v>
       </c>
       <c r="E741" t="s">
-        <v>2326</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="742" spans="1:5" x14ac:dyDescent="0.3">
@@ -20734,7 +20734,7 @@
         <v>1382</v>
       </c>
       <c r="E742" t="s">
-        <v>2326</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="743" spans="1:5" x14ac:dyDescent="0.3">
@@ -20751,7 +20751,7 @@
         <v>1380</v>
       </c>
       <c r="E743" t="s">
-        <v>2326</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="744" spans="1:5" x14ac:dyDescent="0.3">
@@ -20768,7 +20768,7 @@
         <v>1381</v>
       </c>
       <c r="E744" t="s">
-        <v>2326</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="745" spans="1:5" x14ac:dyDescent="0.3">
@@ -20785,7 +20785,7 @@
         <v>1379</v>
       </c>
       <c r="E745" t="s">
-        <v>2326</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="746" spans="1:5" x14ac:dyDescent="0.3">
@@ -20802,7 +20802,7 @@
         <v>1378</v>
       </c>
       <c r="E746" t="s">
-        <v>2326</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="747" spans="1:5" x14ac:dyDescent="0.3">
@@ -20819,7 +20819,7 @@
         <v>1377</v>
       </c>
       <c r="E747" t="s">
-        <v>2326</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="748" spans="1:5" x14ac:dyDescent="0.3">
@@ -20836,7 +20836,7 @@
         <v>1374</v>
       </c>
       <c r="E748" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="749" spans="1:5" x14ac:dyDescent="0.3">
@@ -20853,7 +20853,7 @@
         <v>1373</v>
       </c>
       <c r="E749" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="750" spans="1:5" x14ac:dyDescent="0.3">
@@ -20870,7 +20870,7 @@
         <v>1372</v>
       </c>
       <c r="E750" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="751" spans="1:5" x14ac:dyDescent="0.3">
@@ -20887,7 +20887,7 @@
         <v>1371</v>
       </c>
       <c r="E751" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="752" spans="1:5" x14ac:dyDescent="0.3">
@@ -20904,7 +20904,7 @@
         <v>1370</v>
       </c>
       <c r="E752" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="753" spans="1:5" x14ac:dyDescent="0.3">
@@ -20921,7 +20921,7 @@
         <v>1334</v>
       </c>
       <c r="E753" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="754" spans="1:5" x14ac:dyDescent="0.3">
@@ -20938,7 +20938,7 @@
         <v>1369</v>
       </c>
       <c r="E754" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="755" spans="1:5" x14ac:dyDescent="0.3">
@@ -20955,7 +20955,7 @@
         <v>1368</v>
       </c>
       <c r="E755" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="756" spans="1:5" x14ac:dyDescent="0.3">
@@ -20972,7 +20972,7 @@
         <v>1367</v>
       </c>
       <c r="E756" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="757" spans="1:5" x14ac:dyDescent="0.3">
@@ -20989,7 +20989,7 @@
         <v>1366</v>
       </c>
       <c r="E757" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="758" spans="1:5" x14ac:dyDescent="0.3">
@@ -21006,7 +21006,7 @@
         <v>1365</v>
       </c>
       <c r="E758" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="759" spans="1:5" x14ac:dyDescent="0.3">
@@ -21023,7 +21023,7 @@
         <v>1364</v>
       </c>
       <c r="E759" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="760" spans="1:5" x14ac:dyDescent="0.3">
@@ -21040,7 +21040,7 @@
         <v>1363</v>
       </c>
       <c r="E760" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="761" spans="1:5" x14ac:dyDescent="0.3">
@@ -21057,7 +21057,7 @@
         <v>1362</v>
       </c>
       <c r="E761" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="762" spans="1:5" x14ac:dyDescent="0.3">
@@ -21074,7 +21074,7 @@
         <v>1361</v>
       </c>
       <c r="E762" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="763" spans="1:5" x14ac:dyDescent="0.3">
@@ -21091,7 +21091,7 @@
         <v>1360</v>
       </c>
       <c r="E763" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="764" spans="1:5" x14ac:dyDescent="0.3">
@@ -21108,7 +21108,7 @@
         <v>1359</v>
       </c>
       <c r="E764" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="765" spans="1:5" x14ac:dyDescent="0.3">
@@ -21125,7 +21125,7 @@
         <v>1358</v>
       </c>
       <c r="E765" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="766" spans="1:5" x14ac:dyDescent="0.3">
@@ -21142,7 +21142,7 @@
         <v>1357</v>
       </c>
       <c r="E766" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="767" spans="1:5" x14ac:dyDescent="0.3">
@@ -21159,7 +21159,7 @@
         <v>1356</v>
       </c>
       <c r="E767" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="768" spans="1:5" x14ac:dyDescent="0.3">
@@ -21176,7 +21176,7 @@
         <v>1353</v>
       </c>
       <c r="E768" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="769" spans="1:5" x14ac:dyDescent="0.3">
@@ -21193,7 +21193,7 @@
         <v>1352</v>
       </c>
       <c r="E769" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="770" spans="1:5" x14ac:dyDescent="0.3">
@@ -21210,7 +21210,7 @@
         <v>1334</v>
       </c>
       <c r="E770" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="771" spans="1:5" x14ac:dyDescent="0.3">
@@ -21227,7 +21227,7 @@
         <v>1351</v>
       </c>
       <c r="E771" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="772" spans="1:5" x14ac:dyDescent="0.3">
@@ -21244,7 +21244,7 @@
         <v>1350</v>
       </c>
       <c r="E772" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="773" spans="1:5" x14ac:dyDescent="0.3">
@@ -21261,7 +21261,7 @@
         <v>1349</v>
       </c>
       <c r="E773" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="774" spans="1:5" x14ac:dyDescent="0.3">
@@ -21278,7 +21278,7 @@
         <v>1348</v>
       </c>
       <c r="E774" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="775" spans="1:5" x14ac:dyDescent="0.3">
@@ -21295,7 +21295,7 @@
         <v>1347</v>
       </c>
       <c r="E775" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="776" spans="1:5" x14ac:dyDescent="0.3">
@@ -21312,7 +21312,7 @@
         <v>1344</v>
       </c>
       <c r="E776" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="777" spans="1:5" x14ac:dyDescent="0.3">
@@ -21329,7 +21329,7 @@
         <v>1343</v>
       </c>
       <c r="E777" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="778" spans="1:5" x14ac:dyDescent="0.3">
@@ -21346,7 +21346,7 @@
         <v>1342</v>
       </c>
       <c r="E778" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="779" spans="1:5" x14ac:dyDescent="0.3">
@@ -21363,7 +21363,7 @@
         <v>1341</v>
       </c>
       <c r="E779" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="780" spans="1:5" x14ac:dyDescent="0.3">
@@ -21380,7 +21380,7 @@
         <v>1340</v>
       </c>
       <c r="E780" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="781" spans="1:5" x14ac:dyDescent="0.3">
@@ -21397,7 +21397,7 @@
         <v>1339</v>
       </c>
       <c r="E781" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="782" spans="1:5" x14ac:dyDescent="0.3">
@@ -21414,7 +21414,7 @@
         <v>1338</v>
       </c>
       <c r="E782" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="783" spans="1:5" x14ac:dyDescent="0.3">
@@ -21431,7 +21431,7 @@
         <v>1337</v>
       </c>
       <c r="E783" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="784" spans="1:5" x14ac:dyDescent="0.3">
@@ -21448,7 +21448,7 @@
         <v>1336</v>
       </c>
       <c r="E784" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="785" spans="1:5" x14ac:dyDescent="0.3">
@@ -21465,7 +21465,7 @@
         <v>1335</v>
       </c>
       <c r="E785" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="786" spans="1:5" x14ac:dyDescent="0.3">
@@ -21482,7 +21482,7 @@
         <v>1334</v>
       </c>
       <c r="E786" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="787" spans="1:5" x14ac:dyDescent="0.3">
@@ -21499,7 +21499,7 @@
         <v>1333</v>
       </c>
       <c r="E787" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="788" spans="1:5" x14ac:dyDescent="0.3">
@@ -21516,7 +21516,7 @@
         <v>1332</v>
       </c>
       <c r="E788" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="789" spans="1:5" x14ac:dyDescent="0.3">
@@ -21533,7 +21533,7 @@
         <v>1331</v>
       </c>
       <c r="E789" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="790" spans="1:5" x14ac:dyDescent="0.3">
@@ -21550,7 +21550,7 @@
         <v>1330</v>
       </c>
       <c r="E790" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="791" spans="1:5" x14ac:dyDescent="0.3">
@@ -21567,7 +21567,7 @@
         <v>1329</v>
       </c>
       <c r="E791" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="792" spans="1:5" x14ac:dyDescent="0.3">
@@ -21584,7 +21584,7 @@
         <v>1328</v>
       </c>
       <c r="E792" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="793" spans="1:5" x14ac:dyDescent="0.3">
@@ -21601,7 +21601,7 @@
         <v>1327</v>
       </c>
       <c r="E793" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="794" spans="1:5" x14ac:dyDescent="0.3">
@@ -21618,7 +21618,7 @@
         <v>1324</v>
       </c>
       <c r="E794" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="795" spans="1:5" x14ac:dyDescent="0.3">
@@ -21635,7 +21635,7 @@
         <v>1323</v>
       </c>
       <c r="E795" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="796" spans="1:5" x14ac:dyDescent="0.3">
@@ -21652,7 +21652,7 @@
         <v>1322</v>
       </c>
       <c r="E796" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="797" spans="1:5" x14ac:dyDescent="0.3">
@@ -21669,7 +21669,7 @@
         <v>1321</v>
       </c>
       <c r="E797" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="798" spans="1:5" x14ac:dyDescent="0.3">
@@ -21686,7 +21686,7 @@
         <v>1320</v>
       </c>
       <c r="E798" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="799" spans="1:5" x14ac:dyDescent="0.3">
@@ -21703,7 +21703,7 @@
         <v>1319</v>
       </c>
       <c r="E799" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="800" spans="1:5" x14ac:dyDescent="0.3">
@@ -21720,7 +21720,7 @@
         <v>1318</v>
       </c>
       <c r="E800" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="801" spans="1:5" x14ac:dyDescent="0.3">
@@ -21737,7 +21737,7 @@
         <v>1317</v>
       </c>
       <c r="E801" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="802" spans="1:5" x14ac:dyDescent="0.3">
@@ -21754,7 +21754,7 @@
         <v>1316</v>
       </c>
       <c r="E802" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="803" spans="1:5" x14ac:dyDescent="0.3">
@@ -21771,7 +21771,7 @@
         <v>1315</v>
       </c>
       <c r="E803" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="804" spans="1:5" x14ac:dyDescent="0.3">
@@ -21788,7 +21788,7 @@
         <v>1314</v>
       </c>
       <c r="E804" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="805" spans="1:5" x14ac:dyDescent="0.3">
@@ -21805,7 +21805,7 @@
         <v>1313</v>
       </c>
       <c r="E805" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="806" spans="1:5" x14ac:dyDescent="0.3">
@@ -21822,7 +21822,7 @@
         <v>1312</v>
       </c>
       <c r="E806" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="807" spans="1:5" x14ac:dyDescent="0.3">
@@ -21839,7 +21839,7 @@
         <v>1311</v>
       </c>
       <c r="E807" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="808" spans="1:5" x14ac:dyDescent="0.3">
@@ -21856,7 +21856,7 @@
         <v>1310</v>
       </c>
       <c r="E808" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="809" spans="1:5" x14ac:dyDescent="0.3">
@@ -21873,7 +21873,7 @@
         <v>1307</v>
       </c>
       <c r="E809" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="810" spans="1:5" x14ac:dyDescent="0.3">
@@ -21890,7 +21890,7 @@
         <v>1306</v>
       </c>
       <c r="E810" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="811" spans="1:5" x14ac:dyDescent="0.3">
@@ -21907,7 +21907,7 @@
         <v>1305</v>
       </c>
       <c r="E811" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="812" spans="1:5" x14ac:dyDescent="0.3">
@@ -21924,7 +21924,7 @@
         <v>1304</v>
       </c>
       <c r="E812" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="813" spans="1:5" x14ac:dyDescent="0.3">
@@ -21941,7 +21941,7 @@
         <v>1303</v>
       </c>
       <c r="E813" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="814" spans="1:5" x14ac:dyDescent="0.3">
@@ -21958,7 +21958,7 @@
         <v>1302</v>
       </c>
       <c r="E814" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="815" spans="1:5" x14ac:dyDescent="0.3">
@@ -21975,7 +21975,7 @@
         <v>1301</v>
       </c>
       <c r="E815" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="816" spans="1:5" x14ac:dyDescent="0.3">
@@ -21992,7 +21992,7 @@
         <v>1300</v>
       </c>
       <c r="E816" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="817" spans="1:5" x14ac:dyDescent="0.3">
@@ -22009,7 +22009,7 @@
         <v>1299</v>
       </c>
       <c r="E817" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="818" spans="1:5" x14ac:dyDescent="0.3">
@@ -22026,7 +22026,7 @@
         <v>1298</v>
       </c>
       <c r="E818" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="819" spans="1:5" x14ac:dyDescent="0.3">
@@ -22043,7 +22043,7 @@
         <v>1297</v>
       </c>
       <c r="E819" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="820" spans="1:5" x14ac:dyDescent="0.3">
@@ -22060,7 +22060,7 @@
         <v>1296</v>
       </c>
       <c r="E820" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="821" spans="1:5" x14ac:dyDescent="0.3">
@@ -22077,7 +22077,7 @@
         <v>1295</v>
       </c>
       <c r="E821" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="822" spans="1:5" x14ac:dyDescent="0.3">
@@ -22094,7 +22094,7 @@
         <v>1294</v>
       </c>
       <c r="E822" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="823" spans="1:5" x14ac:dyDescent="0.3">
@@ -22111,7 +22111,7 @@
         <v>1293</v>
       </c>
       <c r="E823" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="824" spans="1:5" x14ac:dyDescent="0.3">
@@ -22128,7 +22128,7 @@
         <v>1292</v>
       </c>
       <c r="E824" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="825" spans="1:5" x14ac:dyDescent="0.3">
@@ -22145,7 +22145,7 @@
         <v>1291</v>
       </c>
       <c r="E825" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="826" spans="1:5" x14ac:dyDescent="0.3">
@@ -22162,7 +22162,7 @@
         <v>1290</v>
       </c>
       <c r="E826" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="827" spans="1:5" x14ac:dyDescent="0.3">
@@ -22179,7 +22179,7 @@
         <v>1289</v>
       </c>
       <c r="E827" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="828" spans="1:5" x14ac:dyDescent="0.3">
@@ -22196,7 +22196,7 @@
         <v>1288</v>
       </c>
       <c r="E828" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="829" spans="1:5" x14ac:dyDescent="0.3">
@@ -22213,7 +22213,7 @@
         <v>1287</v>
       </c>
       <c r="E829" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="830" spans="1:5" x14ac:dyDescent="0.3">
@@ -22230,7 +22230,7 @@
         <v>1286</v>
       </c>
       <c r="E830" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="831" spans="1:5" x14ac:dyDescent="0.3">
@@ -22247,7 +22247,7 @@
         <v>1285</v>
       </c>
       <c r="E831" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="832" spans="1:5" x14ac:dyDescent="0.3">
@@ -22264,7 +22264,7 @@
         <v>1284</v>
       </c>
       <c r="E832" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="833" spans="1:5" x14ac:dyDescent="0.3">
@@ -22281,7 +22281,7 @@
         <v>1283</v>
       </c>
       <c r="E833" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="834" spans="1:5" x14ac:dyDescent="0.3">
@@ -22298,7 +22298,7 @@
         <v>1280</v>
       </c>
       <c r="E834" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="835" spans="1:5" x14ac:dyDescent="0.3">
@@ -22315,7 +22315,7 @@
         <v>1279</v>
       </c>
       <c r="E835" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="836" spans="1:5" x14ac:dyDescent="0.3">
@@ -22332,7 +22332,7 @@
         <v>1278</v>
       </c>
       <c r="E836" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="837" spans="1:5" x14ac:dyDescent="0.3">
@@ -22349,7 +22349,7 @@
         <v>1277</v>
       </c>
       <c r="E837" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="838" spans="1:5" x14ac:dyDescent="0.3">
@@ -22366,7 +22366,7 @@
         <v>1276</v>
       </c>
       <c r="E838" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="839" spans="1:5" x14ac:dyDescent="0.3">
@@ -22383,7 +22383,7 @@
         <v>1275</v>
       </c>
       <c r="E839" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="840" spans="1:5" x14ac:dyDescent="0.3">
@@ -22400,7 +22400,7 @@
         <v>1274</v>
       </c>
       <c r="E840" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="841" spans="1:5" x14ac:dyDescent="0.3">
@@ -22417,7 +22417,7 @@
         <v>1273</v>
       </c>
       <c r="E841" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="842" spans="1:5" x14ac:dyDescent="0.3">
@@ -22434,7 +22434,7 @@
         <v>1272</v>
       </c>
       <c r="E842" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="843" spans="1:5" x14ac:dyDescent="0.3">
@@ -22451,7 +22451,7 @@
         <v>1271</v>
       </c>
       <c r="E843" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="844" spans="1:5" x14ac:dyDescent="0.3">
@@ -22468,7 +22468,7 @@
         <v>1270</v>
       </c>
       <c r="E844" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="845" spans="1:5" x14ac:dyDescent="0.3">
@@ -22485,7 +22485,7 @@
         <v>1269</v>
       </c>
       <c r="E845" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="846" spans="1:5" x14ac:dyDescent="0.3">
@@ -22502,7 +22502,7 @@
         <v>1268</v>
       </c>
       <c r="E846" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="847" spans="1:5" x14ac:dyDescent="0.3">
@@ -22519,7 +22519,7 @@
         <v>1267</v>
       </c>
       <c r="E847" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="848" spans="1:5" x14ac:dyDescent="0.3">
@@ -22536,7 +22536,7 @@
         <v>1266</v>
       </c>
       <c r="E848" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="849" spans="1:5" x14ac:dyDescent="0.3">
@@ -22553,7 +22553,7 @@
         <v>1265</v>
       </c>
       <c r="E849" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="850" spans="1:5" x14ac:dyDescent="0.3">
@@ -22570,7 +22570,7 @@
         <v>1264</v>
       </c>
       <c r="E850" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="851" spans="1:5" x14ac:dyDescent="0.3">
@@ -22587,7 +22587,7 @@
         <v>1263</v>
       </c>
       <c r="E851" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="852" spans="1:5" x14ac:dyDescent="0.3">
@@ -22604,7 +22604,7 @@
         <v>1262</v>
       </c>
       <c r="E852" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="853" spans="1:5" x14ac:dyDescent="0.3">
@@ -22621,7 +22621,7 @@
         <v>1261</v>
       </c>
       <c r="E853" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="854" spans="1:5" x14ac:dyDescent="0.3">
@@ -22638,7 +22638,7 @@
         <v>1260</v>
       </c>
       <c r="E854" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="855" spans="1:5" x14ac:dyDescent="0.3">
@@ -22655,7 +22655,7 @@
         <v>1259</v>
       </c>
       <c r="E855" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="856" spans="1:5" x14ac:dyDescent="0.3">
@@ -22672,7 +22672,7 @@
         <v>1258</v>
       </c>
       <c r="E856" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="857" spans="1:5" x14ac:dyDescent="0.3">
@@ -22689,7 +22689,7 @@
         <v>1257</v>
       </c>
       <c r="E857" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="858" spans="1:5" x14ac:dyDescent="0.3">
@@ -22706,7 +22706,7 @@
         <v>1254</v>
       </c>
       <c r="E858" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="859" spans="1:5" x14ac:dyDescent="0.3">
@@ -22723,7 +22723,7 @@
         <v>1253</v>
       </c>
       <c r="E859" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="860" spans="1:5" x14ac:dyDescent="0.3">
@@ -22740,7 +22740,7 @@
         <v>1252</v>
       </c>
       <c r="E860" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="861" spans="1:5" x14ac:dyDescent="0.3">
@@ -22757,7 +22757,7 @@
         <v>1251</v>
       </c>
       <c r="E861" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="862" spans="1:5" x14ac:dyDescent="0.3">
@@ -22774,7 +22774,7 @@
         <v>1250</v>
       </c>
       <c r="E862" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="863" spans="1:5" x14ac:dyDescent="0.3">
@@ -22791,7 +22791,7 @@
         <v>1249</v>
       </c>
       <c r="E863" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="864" spans="1:5" x14ac:dyDescent="0.3">
@@ -22808,7 +22808,7 @@
         <v>1248</v>
       </c>
       <c r="E864" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="865" spans="1:5" x14ac:dyDescent="0.3">
@@ -22825,7 +22825,7 @@
         <v>1247</v>
       </c>
       <c r="E865" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="866" spans="1:5" x14ac:dyDescent="0.3">
@@ -22842,7 +22842,7 @@
         <v>1246</v>
       </c>
       <c r="E866" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="867" spans="1:5" x14ac:dyDescent="0.3">
@@ -22859,7 +22859,7 @@
         <v>1245</v>
       </c>
       <c r="E867" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="868" spans="1:5" x14ac:dyDescent="0.3">
@@ -22876,7 +22876,7 @@
         <v>1244</v>
       </c>
       <c r="E868" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="869" spans="1:5" x14ac:dyDescent="0.3">
@@ -22893,7 +22893,7 @@
         <v>1243</v>
       </c>
       <c r="E869" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="870" spans="1:5" x14ac:dyDescent="0.3">
@@ -22910,7 +22910,7 @@
         <v>1242</v>
       </c>
       <c r="E870" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="871" spans="1:5" x14ac:dyDescent="0.3">
@@ -22927,7 +22927,7 @@
         <v>1241</v>
       </c>
       <c r="E871" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="872" spans="1:5" x14ac:dyDescent="0.3">
@@ -22944,7 +22944,7 @@
         <v>1240</v>
       </c>
       <c r="E872" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="873" spans="1:5" x14ac:dyDescent="0.3">
@@ -22961,7 +22961,7 @@
         <v>1239</v>
       </c>
       <c r="E873" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="874" spans="1:5" x14ac:dyDescent="0.3">
@@ -22978,7 +22978,7 @@
         <v>1238</v>
       </c>
       <c r="E874" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="875" spans="1:5" x14ac:dyDescent="0.3">
@@ -22995,7 +22995,7 @@
         <v>1237</v>
       </c>
       <c r="E875" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="876" spans="1:5" x14ac:dyDescent="0.3">
@@ -23012,7 +23012,7 @@
         <v>1236</v>
       </c>
       <c r="E876" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="877" spans="1:5" x14ac:dyDescent="0.3">
@@ -23029,7 +23029,7 @@
         <v>1235</v>
       </c>
       <c r="E877" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="878" spans="1:5" x14ac:dyDescent="0.3">
@@ -23046,7 +23046,7 @@
         <v>1234</v>
       </c>
       <c r="E878" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="879" spans="1:5" x14ac:dyDescent="0.3">
@@ -23063,7 +23063,7 @@
         <v>1233</v>
       </c>
       <c r="E879" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="880" spans="1:5" x14ac:dyDescent="0.3">
@@ -23080,7 +23080,7 @@
         <v>1232</v>
       </c>
       <c r="E880" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="881" spans="1:5" x14ac:dyDescent="0.3">
@@ -23097,7 +23097,7 @@
         <v>1231</v>
       </c>
       <c r="E881" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="882" spans="1:5" x14ac:dyDescent="0.3">
@@ -23114,7 +23114,7 @@
         <v>1230</v>
       </c>
       <c r="E882" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="883" spans="1:5" x14ac:dyDescent="0.3">
@@ -23131,7 +23131,7 @@
         <v>1229</v>
       </c>
       <c r="E883" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="884" spans="1:5" x14ac:dyDescent="0.3">
@@ -23148,7 +23148,7 @@
         <v>1228</v>
       </c>
       <c r="E884" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="885" spans="1:5" x14ac:dyDescent="0.3">
@@ -23165,7 +23165,7 @@
         <v>1227</v>
       </c>
       <c r="E885" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="886" spans="1:5" x14ac:dyDescent="0.3">
@@ -23182,7 +23182,7 @@
         <v>1226</v>
       </c>
       <c r="E886" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="887" spans="1:5" x14ac:dyDescent="0.3">
@@ -23199,7 +23199,7 @@
         <v>1225</v>
       </c>
       <c r="E887" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="888" spans="1:5" x14ac:dyDescent="0.3">
@@ -23216,7 +23216,7 @@
         <v>1224</v>
       </c>
       <c r="E888" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="889" spans="1:5" x14ac:dyDescent="0.3">
@@ -23233,7 +23233,7 @@
         <v>1223</v>
       </c>
       <c r="E889" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="890" spans="1:5" x14ac:dyDescent="0.3">
@@ -23250,7 +23250,7 @@
         <v>1220</v>
       </c>
       <c r="E890" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="891" spans="1:5" x14ac:dyDescent="0.3">
@@ -23267,7 +23267,7 @@
         <v>1219</v>
       </c>
       <c r="E891" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="892" spans="1:5" x14ac:dyDescent="0.3">
@@ -23284,7 +23284,7 @@
         <v>1218</v>
       </c>
       <c r="E892" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="893" spans="1:5" x14ac:dyDescent="0.3">
@@ -23301,7 +23301,7 @@
         <v>1217</v>
       </c>
       <c r="E893" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="894" spans="1:5" x14ac:dyDescent="0.3">
@@ -23318,7 +23318,7 @@
         <v>1216</v>
       </c>
       <c r="E894" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="895" spans="1:5" x14ac:dyDescent="0.3">
@@ -23335,7 +23335,7 @@
         <v>1215</v>
       </c>
       <c r="E895" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="896" spans="1:5" x14ac:dyDescent="0.3">
@@ -23352,7 +23352,7 @@
         <v>1214</v>
       </c>
       <c r="E896" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="897" spans="1:5" x14ac:dyDescent="0.3">
@@ -23369,7 +23369,7 @@
         <v>1213</v>
       </c>
       <c r="E897" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="898" spans="1:5" x14ac:dyDescent="0.3">
@@ -23386,7 +23386,7 @@
         <v>1212</v>
       </c>
       <c r="E898" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="899" spans="1:5" x14ac:dyDescent="0.3">
@@ -23403,7 +23403,7 @@
         <v>1211</v>
       </c>
       <c r="E899" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="900" spans="1:5" x14ac:dyDescent="0.3">
@@ -23420,7 +23420,7 @@
         <v>1210</v>
       </c>
       <c r="E900" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="901" spans="1:5" x14ac:dyDescent="0.3">
@@ -23437,7 +23437,7 @@
         <v>1209</v>
       </c>
       <c r="E901" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="902" spans="1:5" x14ac:dyDescent="0.3">
@@ -23454,7 +23454,7 @@
         <v>1208</v>
       </c>
       <c r="E902" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="903" spans="1:5" x14ac:dyDescent="0.3">
@@ -23471,7 +23471,7 @@
         <v>1207</v>
       </c>
       <c r="E903" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="904" spans="1:5" x14ac:dyDescent="0.3">
@@ -23488,7 +23488,7 @@
         <v>1206</v>
       </c>
       <c r="E904" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="905" spans="1:5" x14ac:dyDescent="0.3">
@@ -23505,7 +23505,7 @@
         <v>1205</v>
       </c>
       <c r="E905" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="906" spans="1:5" x14ac:dyDescent="0.3">
@@ -23522,7 +23522,7 @@
         <v>1204</v>
       </c>
       <c r="E906" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="907" spans="1:5" x14ac:dyDescent="0.3">
@@ -23539,7 +23539,7 @@
         <v>1203</v>
       </c>
       <c r="E907" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="908" spans="1:5" x14ac:dyDescent="0.3">
@@ -23556,7 +23556,7 @@
         <v>1202</v>
       </c>
       <c r="E908" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="909" spans="1:5" x14ac:dyDescent="0.3">
@@ -23573,7 +23573,7 @@
         <v>1201</v>
       </c>
       <c r="E909" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="910" spans="1:5" x14ac:dyDescent="0.3">
@@ -23590,7 +23590,7 @@
         <v>1200</v>
       </c>
       <c r="E910" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="911" spans="1:5" x14ac:dyDescent="0.3">
@@ -23607,7 +23607,7 @@
         <v>1199</v>
       </c>
       <c r="E911" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="912" spans="1:5" x14ac:dyDescent="0.3">
@@ -23624,7 +23624,7 @@
         <v>1198</v>
       </c>
       <c r="E912" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="913" spans="1:5" x14ac:dyDescent="0.3">
@@ -23641,7 +23641,7 @@
         <v>1197</v>
       </c>
       <c r="E913" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="914" spans="1:5" x14ac:dyDescent="0.3">
@@ -23658,7 +23658,7 @@
         <v>1196</v>
       </c>
       <c r="E914" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="915" spans="1:5" x14ac:dyDescent="0.3">
@@ -23675,7 +23675,7 @@
         <v>1195</v>
       </c>
       <c r="E915" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="916" spans="1:5" x14ac:dyDescent="0.3">
@@ -23692,7 +23692,7 @@
         <v>1194</v>
       </c>
       <c r="E916" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="917" spans="1:5" x14ac:dyDescent="0.3">
@@ -23709,7 +23709,7 @@
         <v>1193</v>
       </c>
       <c r="E917" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="918" spans="1:5" x14ac:dyDescent="0.3">
@@ -23726,7 +23726,7 @@
         <v>1192</v>
       </c>
       <c r="E918" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="919" spans="1:5" x14ac:dyDescent="0.3">
@@ -23743,7 +23743,7 @@
         <v>1191</v>
       </c>
       <c r="E919" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="920" spans="1:5" x14ac:dyDescent="0.3">
@@ -23760,7 +23760,7 @@
         <v>1190</v>
       </c>
       <c r="E920" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="921" spans="1:5" x14ac:dyDescent="0.3">
@@ -23777,7 +23777,7 @@
         <v>1189</v>
       </c>
       <c r="E921" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="922" spans="1:5" x14ac:dyDescent="0.3">
@@ -23794,7 +23794,7 @@
         <v>1188</v>
       </c>
       <c r="E922" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="923" spans="1:5" x14ac:dyDescent="0.3">
@@ -23811,7 +23811,7 @@
         <v>1187</v>
       </c>
       <c r="E923" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="924" spans="1:5" x14ac:dyDescent="0.3">
@@ -23828,7 +23828,7 @@
         <v>1186</v>
       </c>
       <c r="E924" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="925" spans="1:5" x14ac:dyDescent="0.3">
@@ -23845,7 +23845,7 @@
         <v>1183</v>
       </c>
       <c r="E925" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="926" spans="1:5" x14ac:dyDescent="0.3">
@@ -23862,7 +23862,7 @@
         <v>1182</v>
       </c>
       <c r="E926" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="927" spans="1:5" x14ac:dyDescent="0.3">
@@ -23879,7 +23879,7 @@
         <v>1181</v>
       </c>
       <c r="E927" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="928" spans="1:5" x14ac:dyDescent="0.3">
@@ -23896,7 +23896,7 @@
         <v>1180</v>
       </c>
       <c r="E928" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="929" spans="1:5" x14ac:dyDescent="0.3">
@@ -23913,7 +23913,7 @@
         <v>1179</v>
       </c>
       <c r="E929" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="930" spans="1:5" x14ac:dyDescent="0.3">
@@ -23930,7 +23930,7 @@
         <v>1178</v>
       </c>
       <c r="E930" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="931" spans="1:5" x14ac:dyDescent="0.3">
@@ -23947,7 +23947,7 @@
         <v>1177</v>
       </c>
       <c r="E931" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="932" spans="1:5" x14ac:dyDescent="0.3">
@@ -23964,7 +23964,7 @@
         <v>1176</v>
       </c>
       <c r="E932" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="933" spans="1:5" x14ac:dyDescent="0.3">
@@ -23981,7 +23981,7 @@
         <v>1175</v>
       </c>
       <c r="E933" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="934" spans="1:5" x14ac:dyDescent="0.3">
@@ -23998,7 +23998,7 @@
         <v>1174</v>
       </c>
       <c r="E934" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="935" spans="1:5" x14ac:dyDescent="0.3">
@@ -24015,7 +24015,7 @@
         <v>1173</v>
       </c>
       <c r="E935" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="936" spans="1:5" x14ac:dyDescent="0.3">
@@ -24032,7 +24032,7 @@
         <v>1172</v>
       </c>
       <c r="E936" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="937" spans="1:5" x14ac:dyDescent="0.3">
@@ -24049,7 +24049,7 @@
         <v>1171</v>
       </c>
       <c r="E937" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="938" spans="1:5" x14ac:dyDescent="0.3">
@@ -24066,7 +24066,7 @@
         <v>1170</v>
       </c>
       <c r="E938" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="939" spans="1:5" x14ac:dyDescent="0.3">
@@ -24083,7 +24083,7 @@
         <v>1169</v>
       </c>
       <c r="E939" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="940" spans="1:5" x14ac:dyDescent="0.3">
@@ -24100,7 +24100,7 @@
         <v>1168</v>
       </c>
       <c r="E940" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="941" spans="1:5" x14ac:dyDescent="0.3">
@@ -24117,7 +24117,7 @@
         <v>1167</v>
       </c>
       <c r="E941" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="942" spans="1:5" x14ac:dyDescent="0.3">
@@ -24134,7 +24134,7 @@
         <v>1166</v>
       </c>
       <c r="E942" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="943" spans="1:5" x14ac:dyDescent="0.3">
@@ -24151,7 +24151,7 @@
         <v>1165</v>
       </c>
       <c r="E943" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="944" spans="1:5" x14ac:dyDescent="0.3">
@@ -24168,7 +24168,7 @@
         <v>1162</v>
       </c>
       <c r="E944" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="945" spans="1:5" x14ac:dyDescent="0.3">
@@ -24185,7 +24185,7 @@
         <v>1161</v>
       </c>
       <c r="E945" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="946" spans="1:5" x14ac:dyDescent="0.3">
@@ -24202,7 +24202,7 @@
         <v>1160</v>
       </c>
       <c r="E946" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="947" spans="1:5" x14ac:dyDescent="0.3">
@@ -24219,7 +24219,7 @@
         <v>1159</v>
       </c>
       <c r="E947" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="948" spans="1:5" x14ac:dyDescent="0.3">
@@ -24236,7 +24236,7 @@
         <v>1158</v>
       </c>
       <c r="E948" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="949" spans="1:5" x14ac:dyDescent="0.3">
@@ -24253,7 +24253,7 @@
         <v>1157</v>
       </c>
       <c r="E949" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="950" spans="1:5" x14ac:dyDescent="0.3">
@@ -24270,7 +24270,7 @@
         <v>1156</v>
       </c>
       <c r="E950" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="951" spans="1:5" x14ac:dyDescent="0.3">
@@ -24287,7 +24287,7 @@
         <v>1155</v>
       </c>
       <c r="E951" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="952" spans="1:5" x14ac:dyDescent="0.3">
@@ -24304,7 +24304,7 @@
         <v>1154</v>
       </c>
       <c r="E952" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="953" spans="1:5" x14ac:dyDescent="0.3">
@@ -24321,7 +24321,7 @@
         <v>1153</v>
       </c>
       <c r="E953" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="954" spans="1:5" x14ac:dyDescent="0.3">
@@ -24338,7 +24338,7 @@
         <v>1152</v>
       </c>
       <c r="E954" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="955" spans="1:5" x14ac:dyDescent="0.3">
@@ -24355,7 +24355,7 @@
         <v>1151</v>
       </c>
       <c r="E955" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="956" spans="1:5" x14ac:dyDescent="0.3">
@@ -24372,7 +24372,7 @@
         <v>1150</v>
       </c>
       <c r="E956" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="957" spans="1:5" x14ac:dyDescent="0.3">
@@ -24389,7 +24389,7 @@
         <v>1147</v>
       </c>
       <c r="E957" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="958" spans="1:5" x14ac:dyDescent="0.3">
@@ -24406,7 +24406,7 @@
         <v>1146</v>
       </c>
       <c r="E958" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="959" spans="1:5" x14ac:dyDescent="0.3">
@@ -24423,7 +24423,7 @@
         <v>1145</v>
       </c>
       <c r="E959" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="960" spans="1:5" x14ac:dyDescent="0.3">
@@ -24440,7 +24440,7 @@
         <v>1144</v>
       </c>
       <c r="E960" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="961" spans="1:5" x14ac:dyDescent="0.3">
@@ -24457,7 +24457,7 @@
         <v>1143</v>
       </c>
       <c r="E961" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="962" spans="1:5" x14ac:dyDescent="0.3">
@@ -24474,7 +24474,7 @@
         <v>1142</v>
       </c>
       <c r="E962" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="963" spans="1:5" x14ac:dyDescent="0.3">
@@ -24491,7 +24491,7 @@
         <v>1141</v>
       </c>
       <c r="E963" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="964" spans="1:5" x14ac:dyDescent="0.3">
@@ -24508,7 +24508,7 @@
         <v>1140</v>
       </c>
       <c r="E964" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="965" spans="1:5" x14ac:dyDescent="0.3">
@@ -24525,7 +24525,7 @@
         <v>1139</v>
       </c>
       <c r="E965" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="966" spans="1:5" x14ac:dyDescent="0.3">
@@ -24542,7 +24542,7 @@
         <v>1138</v>
       </c>
       <c r="E966" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="967" spans="1:5" x14ac:dyDescent="0.3">
@@ -24559,7 +24559,7 @@
         <v>1137</v>
       </c>
       <c r="E967" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="968" spans="1:5" x14ac:dyDescent="0.3">
@@ -24576,7 +24576,7 @@
         <v>1136</v>
       </c>
       <c r="E968" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="969" spans="1:5" x14ac:dyDescent="0.3">
@@ -24593,7 +24593,7 @@
         <v>1135</v>
       </c>
       <c r="E969" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="970" spans="1:5" x14ac:dyDescent="0.3">
@@ -24610,7 +24610,7 @@
         <v>1134</v>
       </c>
       <c r="E970" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="971" spans="1:5" x14ac:dyDescent="0.3">
@@ -24627,7 +24627,7 @@
         <v>1133</v>
       </c>
       <c r="E971" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="972" spans="1:5" x14ac:dyDescent="0.3">
@@ -24644,7 +24644,7 @@
         <v>1132</v>
       </c>
       <c r="E972" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="973" spans="1:5" x14ac:dyDescent="0.3">
@@ -24661,7 +24661,7 @@
         <v>1131</v>
       </c>
       <c r="E973" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="974" spans="1:5" x14ac:dyDescent="0.3">
@@ -24678,7 +24678,7 @@
         <v>1130</v>
       </c>
       <c r="E974" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="975" spans="1:5" x14ac:dyDescent="0.3">
@@ -24695,7 +24695,7 @@
         <v>1129</v>
       </c>
       <c r="E975" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="976" spans="1:5" x14ac:dyDescent="0.3">
@@ -24712,7 +24712,7 @@
         <v>1128</v>
       </c>
       <c r="E976" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="977" spans="1:5" x14ac:dyDescent="0.3">
@@ -24729,7 +24729,7 @@
         <v>1127</v>
       </c>
       <c r="E977" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="978" spans="1:5" x14ac:dyDescent="0.3">
@@ -24746,7 +24746,7 @@
         <v>1126</v>
       </c>
       <c r="E978" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="979" spans="1:5" x14ac:dyDescent="0.3">
@@ -24763,7 +24763,7 @@
         <v>1125</v>
       </c>
       <c r="E979" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="980" spans="1:5" x14ac:dyDescent="0.3">
@@ -24780,7 +24780,7 @@
         <v>1122</v>
       </c>
       <c r="E980" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="981" spans="1:5" x14ac:dyDescent="0.3">
@@ -24797,7 +24797,7 @@
         <v>1121</v>
       </c>
       <c r="E981" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="982" spans="1:5" x14ac:dyDescent="0.3">
@@ -24814,7 +24814,7 @@
         <v>1120</v>
       </c>
       <c r="E982" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="983" spans="1:5" x14ac:dyDescent="0.3">
@@ -24831,7 +24831,7 @@
         <v>1119</v>
       </c>
       <c r="E983" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="984" spans="1:5" x14ac:dyDescent="0.3">
@@ -24848,7 +24848,7 @@
         <v>1118</v>
       </c>
       <c r="E984" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="985" spans="1:5" x14ac:dyDescent="0.3">
@@ -24865,7 +24865,7 @@
         <v>1117</v>
       </c>
       <c r="E985" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="986" spans="1:5" x14ac:dyDescent="0.3">
@@ -24882,7 +24882,7 @@
         <v>1116</v>
       </c>
       <c r="E986" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="987" spans="1:5" x14ac:dyDescent="0.3">
@@ -24899,7 +24899,7 @@
         <v>1115</v>
       </c>
       <c r="E987" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="988" spans="1:5" x14ac:dyDescent="0.3">
@@ -24916,7 +24916,7 @@
         <v>1114</v>
       </c>
       <c r="E988" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="989" spans="1:5" x14ac:dyDescent="0.3">
@@ -24933,7 +24933,7 @@
         <v>1113</v>
       </c>
       <c r="E989" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="990" spans="1:5" x14ac:dyDescent="0.3">
@@ -24950,7 +24950,7 @@
         <v>1112</v>
       </c>
       <c r="E990" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="991" spans="1:5" x14ac:dyDescent="0.3">
@@ -24967,7 +24967,7 @@
         <v>1111</v>
       </c>
       <c r="E991" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="992" spans="1:5" x14ac:dyDescent="0.3">
@@ -24984,7 +24984,7 @@
         <v>1110</v>
       </c>
       <c r="E992" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="993" spans="1:5" x14ac:dyDescent="0.3">
@@ -25001,7 +25001,7 @@
         <v>1109</v>
       </c>
       <c r="E993" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="994" spans="1:5" x14ac:dyDescent="0.3">
@@ -25018,7 +25018,7 @@
         <v>1108</v>
       </c>
       <c r="E994" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="995" spans="1:5" x14ac:dyDescent="0.3">
@@ -25035,7 +25035,7 @@
         <v>1107</v>
       </c>
       <c r="E995" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="996" spans="1:5" x14ac:dyDescent="0.3">
@@ -25052,7 +25052,7 @@
         <v>1106</v>
       </c>
       <c r="E996" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="997" spans="1:5" x14ac:dyDescent="0.3">
@@ -25069,7 +25069,7 @@
         <v>1105</v>
       </c>
       <c r="E997" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="998" spans="1:5" x14ac:dyDescent="0.3">
@@ -25086,7 +25086,7 @@
         <v>1104</v>
       </c>
       <c r="E998" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="999" spans="1:5" x14ac:dyDescent="0.3">
@@ -25103,7 +25103,7 @@
         <v>1103</v>
       </c>
       <c r="E999" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="1000" spans="1:5" x14ac:dyDescent="0.3">
@@ -25120,7 +25120,7 @@
         <v>1102</v>
       </c>
       <c r="E1000" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="1001" spans="1:5" x14ac:dyDescent="0.3">
@@ -25137,7 +25137,7 @@
         <v>1101</v>
       </c>
       <c r="E1001" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="1002" spans="1:5" x14ac:dyDescent="0.3">
@@ -25154,7 +25154,7 @@
         <v>1100</v>
       </c>
       <c r="E1002" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="1003" spans="1:5" x14ac:dyDescent="0.3">
@@ -25171,7 +25171,7 @@
         <v>1099</v>
       </c>
       <c r="E1003" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="1004" spans="1:5" x14ac:dyDescent="0.3">
@@ -25188,7 +25188,7 @@
         <v>1098</v>
       </c>
       <c r="E1004" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="1005" spans="1:5" x14ac:dyDescent="0.3">
@@ -25205,7 +25205,7 @@
         <v>1097</v>
       </c>
       <c r="E1005" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="1006" spans="1:5" x14ac:dyDescent="0.3">
@@ -25222,7 +25222,7 @@
         <v>1096</v>
       </c>
       <c r="E1006" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="1007" spans="1:5" x14ac:dyDescent="0.3">
@@ -25239,7 +25239,7 @@
         <v>1093</v>
       </c>
       <c r="E1007" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1008" spans="1:5" x14ac:dyDescent="0.3">
@@ -25256,7 +25256,7 @@
         <v>1092</v>
       </c>
       <c r="E1008" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1009" spans="1:5" x14ac:dyDescent="0.3">
@@ -25273,7 +25273,7 @@
         <v>1091</v>
       </c>
       <c r="E1009" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1010" spans="1:5" x14ac:dyDescent="0.3">
@@ -25290,7 +25290,7 @@
         <v>1090</v>
       </c>
       <c r="E1010" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1011" spans="1:5" x14ac:dyDescent="0.3">
@@ -25307,7 +25307,7 @@
         <v>1089</v>
       </c>
       <c r="E1011" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1012" spans="1:5" x14ac:dyDescent="0.3">
@@ -25324,7 +25324,7 @@
         <v>1088</v>
       </c>
       <c r="E1012" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1013" spans="1:5" x14ac:dyDescent="0.3">
@@ -25341,7 +25341,7 @@
         <v>1087</v>
       </c>
       <c r="E1013" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1014" spans="1:5" x14ac:dyDescent="0.3">
@@ -25358,7 +25358,7 @@
         <v>1086</v>
       </c>
       <c r="E1014" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1015" spans="1:5" x14ac:dyDescent="0.3">
@@ -25375,7 +25375,7 @@
         <v>1085</v>
       </c>
       <c r="E1015" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1016" spans="1:5" x14ac:dyDescent="0.3">
@@ -25392,7 +25392,7 @@
         <v>1084</v>
       </c>
       <c r="E1016" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1017" spans="1:5" x14ac:dyDescent="0.3">
@@ -25409,7 +25409,7 @@
         <v>1083</v>
       </c>
       <c r="E1017" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1018" spans="1:5" x14ac:dyDescent="0.3">
@@ -25426,7 +25426,7 @@
         <v>1082</v>
       </c>
       <c r="E1018" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1019" spans="1:5" x14ac:dyDescent="0.3">
@@ -25443,7 +25443,7 @@
         <v>1081</v>
       </c>
       <c r="E1019" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1020" spans="1:5" x14ac:dyDescent="0.3">
@@ -25460,7 +25460,7 @@
         <v>1080</v>
       </c>
       <c r="E1020" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1021" spans="1:5" x14ac:dyDescent="0.3">
@@ -25477,7 +25477,7 @@
         <v>1079</v>
       </c>
       <c r="E1021" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1022" spans="1:5" x14ac:dyDescent="0.3">
@@ -25494,7 +25494,7 @@
         <v>1078</v>
       </c>
       <c r="E1022" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1023" spans="1:5" x14ac:dyDescent="0.3">
@@ -25511,7 +25511,7 @@
         <v>1077</v>
       </c>
       <c r="E1023" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1024" spans="1:5" x14ac:dyDescent="0.3">
@@ -25528,7 +25528,7 @@
         <v>1076</v>
       </c>
       <c r="E1024" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1025" spans="1:5" x14ac:dyDescent="0.3">
@@ -25545,7 +25545,7 @@
         <v>1075</v>
       </c>
       <c r="E1025" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1026" spans="1:5" x14ac:dyDescent="0.3">
@@ -25562,7 +25562,7 @@
         <v>1074</v>
       </c>
       <c r="E1026" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1027" spans="1:5" x14ac:dyDescent="0.3">
@@ -25579,7 +25579,7 @@
         <v>1073</v>
       </c>
       <c r="E1027" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1028" spans="1:5" x14ac:dyDescent="0.3">
@@ -25596,7 +25596,7 @@
         <v>1072</v>
       </c>
       <c r="E1028" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1029" spans="1:5" x14ac:dyDescent="0.3">
@@ -25613,7 +25613,7 @@
         <v>1071</v>
       </c>
       <c r="E1029" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1030" spans="1:5" x14ac:dyDescent="0.3">
@@ -25630,7 +25630,7 @@
         <v>1049</v>
       </c>
       <c r="E1030" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1031" spans="1:5" x14ac:dyDescent="0.3">
@@ -25647,7 +25647,7 @@
         <v>1048</v>
       </c>
       <c r="E1031" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1032" spans="1:5" x14ac:dyDescent="0.3">
@@ -25664,7 +25664,7 @@
         <v>1047</v>
       </c>
       <c r="E1032" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1033" spans="1:5" x14ac:dyDescent="0.3">
@@ -25681,7 +25681,7 @@
         <v>1046</v>
       </c>
       <c r="E1033" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1034" spans="1:5" x14ac:dyDescent="0.3">
@@ -25698,7 +25698,7 @@
         <v>1045</v>
       </c>
       <c r="E1034" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1035" spans="1:5" x14ac:dyDescent="0.3">
@@ -25715,7 +25715,7 @@
         <v>1044</v>
       </c>
       <c r="E1035" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1036" spans="1:5" x14ac:dyDescent="0.3">
@@ -25732,7 +25732,7 @@
         <v>1043</v>
       </c>
       <c r="E1036" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1037" spans="1:5" x14ac:dyDescent="0.3">
@@ -25749,7 +25749,7 @@
         <v>1042</v>
       </c>
       <c r="E1037" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1038" spans="1:5" x14ac:dyDescent="0.3">
@@ -25766,7 +25766,7 @@
         <v>1041</v>
       </c>
       <c r="E1038" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1039" spans="1:5" x14ac:dyDescent="0.3">
@@ -25783,7 +25783,7 @@
         <v>1040</v>
       </c>
       <c r="E1039" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1040" spans="1:5" x14ac:dyDescent="0.3">
@@ -25800,7 +25800,7 @@
         <v>1039</v>
       </c>
       <c r="E1040" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1041" spans="1:5" x14ac:dyDescent="0.3">
@@ -25817,7 +25817,7 @@
         <v>1038</v>
       </c>
       <c r="E1041" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1042" spans="1:5" x14ac:dyDescent="0.3">
@@ -25834,7 +25834,7 @@
         <v>1037</v>
       </c>
       <c r="E1042" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1043" spans="1:5" x14ac:dyDescent="0.3">
@@ -25851,7 +25851,7 @@
         <v>1036</v>
       </c>
       <c r="E1043" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1044" spans="1:5" x14ac:dyDescent="0.3">
@@ -25868,7 +25868,7 @@
         <v>1035</v>
       </c>
       <c r="E1044" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1045" spans="1:5" x14ac:dyDescent="0.3">
@@ -25885,7 +25885,7 @@
         <v>1034</v>
       </c>
       <c r="E1045" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1046" spans="1:5" x14ac:dyDescent="0.3">
@@ -25902,7 +25902,7 @@
         <v>1033</v>
       </c>
       <c r="E1046" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1047" spans="1:5" x14ac:dyDescent="0.3">
@@ -25919,7 +25919,7 @@
         <v>1032</v>
       </c>
       <c r="E1047" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1048" spans="1:5" x14ac:dyDescent="0.3">
@@ -25936,7 +25936,7 @@
         <v>1031</v>
       </c>
       <c r="E1048" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1049" spans="1:5" x14ac:dyDescent="0.3">
@@ -25953,7 +25953,7 @@
         <v>1030</v>
       </c>
       <c r="E1049" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1050" spans="1:5" x14ac:dyDescent="0.3">
@@ -25970,7 +25970,7 @@
         <v>1029</v>
       </c>
       <c r="E1050" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1051" spans="1:5" x14ac:dyDescent="0.3">
@@ -25987,7 +25987,7 @@
         <v>1028</v>
       </c>
       <c r="E1051" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1052" spans="1:5" x14ac:dyDescent="0.3">
@@ -26004,7 +26004,7 @@
         <v>1027</v>
       </c>
       <c r="E1052" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1053" spans="1:5" x14ac:dyDescent="0.3">
@@ -26021,7 +26021,7 @@
         <v>1026</v>
       </c>
       <c r="E1053" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1054" spans="1:5" x14ac:dyDescent="0.3">
@@ -26038,7 +26038,7 @@
         <v>1025</v>
       </c>
       <c r="E1054" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1055" spans="1:5" x14ac:dyDescent="0.3">
@@ -26055,7 +26055,7 @@
         <v>1024</v>
       </c>
       <c r="E1055" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1056" spans="1:5" x14ac:dyDescent="0.3">
@@ -26072,7 +26072,7 @@
         <v>1023</v>
       </c>
       <c r="E1056" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1057" spans="1:5" x14ac:dyDescent="0.3">
@@ -26089,7 +26089,7 @@
         <v>1022</v>
       </c>
       <c r="E1057" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1058" spans="1:5" x14ac:dyDescent="0.3">
@@ -26106,7 +26106,7 @@
         <v>1021</v>
       </c>
       <c r="E1058" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1059" spans="1:5" x14ac:dyDescent="0.3">
@@ -26123,7 +26123,7 @@
         <v>1020</v>
       </c>
       <c r="E1059" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1060" spans="1:5" x14ac:dyDescent="0.3">
@@ -26140,7 +26140,7 @@
         <v>1019</v>
       </c>
       <c r="E1060" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1061" spans="1:5" x14ac:dyDescent="0.3">
@@ -26157,7 +26157,7 @@
         <v>1018</v>
       </c>
       <c r="E1061" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1062" spans="1:5" x14ac:dyDescent="0.3">
@@ -26174,7 +26174,7 @@
         <v>1017</v>
       </c>
       <c r="E1062" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1063" spans="1:5" x14ac:dyDescent="0.3">
@@ -26191,7 +26191,7 @@
         <v>1016</v>
       </c>
       <c r="E1063" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1064" spans="1:5" x14ac:dyDescent="0.3">
@@ -26208,7 +26208,7 @@
         <v>1015</v>
       </c>
       <c r="E1064" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1065" spans="1:5" x14ac:dyDescent="0.3">
@@ -26225,7 +26225,7 @@
         <v>1068</v>
       </c>
       <c r="E1065" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1066" spans="1:5" x14ac:dyDescent="0.3">
@@ -26242,7 +26242,7 @@
         <v>1067</v>
       </c>
       <c r="E1066" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1067" spans="1:5" x14ac:dyDescent="0.3">
@@ -26259,7 +26259,7 @@
         <v>1066</v>
       </c>
       <c r="E1067" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1068" spans="1:5" x14ac:dyDescent="0.3">
@@ -26276,7 +26276,7 @@
         <v>1065</v>
       </c>
       <c r="E1068" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1069" spans="1:5" x14ac:dyDescent="0.3">
@@ -26293,7 +26293,7 @@
         <v>1064</v>
       </c>
       <c r="E1069" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1070" spans="1:5" x14ac:dyDescent="0.3">
@@ -26310,7 +26310,7 @@
         <v>1063</v>
       </c>
       <c r="E1070" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1071" spans="1:5" x14ac:dyDescent="0.3">
@@ -26327,7 +26327,7 @@
         <v>1062</v>
       </c>
       <c r="E1071" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1072" spans="1:5" x14ac:dyDescent="0.3">
@@ -26344,7 +26344,7 @@
         <v>1061</v>
       </c>
       <c r="E1072" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1073" spans="1:5" x14ac:dyDescent="0.3">
@@ -26361,7 +26361,7 @@
         <v>1060</v>
       </c>
       <c r="E1073" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1074" spans="1:5" x14ac:dyDescent="0.3">
@@ -26378,7 +26378,7 @@
         <v>1059</v>
       </c>
       <c r="E1074" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1075" spans="1:5" x14ac:dyDescent="0.3">
@@ -26395,7 +26395,7 @@
         <v>1058</v>
       </c>
       <c r="E1075" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1076" spans="1:5" x14ac:dyDescent="0.3">
@@ -26412,7 +26412,7 @@
         <v>1057</v>
       </c>
       <c r="E1076" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1077" spans="1:5" x14ac:dyDescent="0.3">
@@ -26429,7 +26429,7 @@
         <v>1056</v>
       </c>
       <c r="E1077" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1078" spans="1:5" x14ac:dyDescent="0.3">
@@ -26446,7 +26446,7 @@
         <v>1055</v>
       </c>
       <c r="E1078" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1079" spans="1:5" x14ac:dyDescent="0.3">
@@ -26463,7 +26463,7 @@
         <v>1054</v>
       </c>
       <c r="E1079" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1080" spans="1:5" x14ac:dyDescent="0.3">
@@ -26480,7 +26480,7 @@
         <v>1053</v>
       </c>
       <c r="E1080" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1081" spans="1:5" x14ac:dyDescent="0.3">
@@ -26497,7 +26497,7 @@
         <v>1052</v>
       </c>
       <c r="E1081" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1082" spans="1:5" x14ac:dyDescent="0.3">
@@ -26514,7 +26514,7 @@
         <v>1012</v>
       </c>
       <c r="E1082" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1083" spans="1:5" x14ac:dyDescent="0.3">
@@ -26531,7 +26531,7 @@
         <v>1011</v>
       </c>
       <c r="E1083" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1084" spans="1:5" x14ac:dyDescent="0.3">
@@ -26548,7 +26548,7 @@
         <v>1010</v>
       </c>
       <c r="E1084" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1085" spans="1:5" x14ac:dyDescent="0.3">
@@ -26565,7 +26565,7 @@
         <v>1009</v>
       </c>
       <c r="E1085" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1086" spans="1:5" x14ac:dyDescent="0.3">
@@ -26582,7 +26582,7 @@
         <v>1008</v>
       </c>
       <c r="E1086" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1087" spans="1:5" x14ac:dyDescent="0.3">
@@ -26599,7 +26599,7 @@
         <v>1007</v>
       </c>
       <c r="E1087" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1088" spans="1:5" x14ac:dyDescent="0.3">
@@ -26616,7 +26616,7 @@
         <v>1006</v>
       </c>
       <c r="E1088" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1089" spans="1:5" x14ac:dyDescent="0.3">
@@ -26633,7 +26633,7 @@
         <v>1005</v>
       </c>
       <c r="E1089" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1090" spans="1:5" x14ac:dyDescent="0.3">
@@ -26650,7 +26650,7 @@
         <v>1004</v>
       </c>
       <c r="E1090" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1091" spans="1:5" x14ac:dyDescent="0.3">
@@ -26667,7 +26667,7 @@
         <v>1003</v>
       </c>
       <c r="E1091" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1092" spans="1:5" x14ac:dyDescent="0.3">
@@ -26684,7 +26684,7 @@
         <v>1002</v>
       </c>
       <c r="E1092" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1093" spans="1:5" x14ac:dyDescent="0.3">
@@ -26701,7 +26701,7 @@
         <v>1001</v>
       </c>
       <c r="E1093" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1094" spans="1:5" x14ac:dyDescent="0.3">
@@ -26718,7 +26718,7 @@
         <v>1000</v>
       </c>
       <c r="E1094" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1095" spans="1:5" x14ac:dyDescent="0.3">
@@ -26735,7 +26735,7 @@
         <v>999</v>
       </c>
       <c r="E1095" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1096" spans="1:5" x14ac:dyDescent="0.3">
@@ -26752,7 +26752,7 @@
         <v>998</v>
       </c>
       <c r="E1096" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1097" spans="1:5" x14ac:dyDescent="0.3">
@@ -26769,7 +26769,7 @@
         <v>997</v>
       </c>
       <c r="E1097" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1098" spans="1:5" x14ac:dyDescent="0.3">
@@ -26786,7 +26786,7 @@
         <v>996</v>
       </c>
       <c r="E1098" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1099" spans="1:5" x14ac:dyDescent="0.3">
@@ -26803,7 +26803,7 @@
         <v>995</v>
       </c>
       <c r="E1099" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1100" spans="1:5" x14ac:dyDescent="0.3">
@@ -26820,7 +26820,7 @@
         <v>994</v>
       </c>
       <c r="E1100" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1101" spans="1:5" x14ac:dyDescent="0.3">
@@ -26837,7 +26837,7 @@
         <v>993</v>
       </c>
       <c r="E1101" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1102" spans="1:5" x14ac:dyDescent="0.3">
@@ -26854,7 +26854,7 @@
         <v>992</v>
       </c>
       <c r="E1102" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1103" spans="1:5" x14ac:dyDescent="0.3">
@@ -26871,7 +26871,7 @@
         <v>991</v>
       </c>
       <c r="E1103" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1104" spans="1:5" x14ac:dyDescent="0.3">
@@ -26888,7 +26888,7 @@
         <v>990</v>
       </c>
       <c r="E1104" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1105" spans="1:5" x14ac:dyDescent="0.3">
@@ -26905,7 +26905,7 @@
         <v>989</v>
       </c>
       <c r="E1105" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1106" spans="1:5" x14ac:dyDescent="0.3">
@@ -26922,7 +26922,7 @@
         <v>988</v>
       </c>
       <c r="E1106" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1107" spans="1:5" x14ac:dyDescent="0.3">
@@ -26939,7 +26939,7 @@
         <v>987</v>
       </c>
       <c r="E1107" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1108" spans="1:5" x14ac:dyDescent="0.3">
@@ -26956,7 +26956,7 @@
         <v>986</v>
       </c>
       <c r="E1108" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1109" spans="1:5" x14ac:dyDescent="0.3">
@@ -26973,7 +26973,7 @@
         <v>985</v>
       </c>
       <c r="E1109" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1110" spans="1:5" x14ac:dyDescent="0.3">
@@ -26990,7 +26990,7 @@
         <v>982</v>
       </c>
       <c r="E1110" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1111" spans="1:5" x14ac:dyDescent="0.3">
@@ -27007,7 +27007,7 @@
         <v>981</v>
       </c>
       <c r="E1111" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1112" spans="1:5" x14ac:dyDescent="0.3">
@@ -27024,7 +27024,7 @@
         <v>980</v>
       </c>
       <c r="E1112" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1113" spans="1:5" x14ac:dyDescent="0.3">
@@ -27041,7 +27041,7 @@
         <v>979</v>
       </c>
       <c r="E1113" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1114" spans="1:5" x14ac:dyDescent="0.3">
@@ -27058,7 +27058,7 @@
         <v>978</v>
       </c>
       <c r="E1114" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1115" spans="1:5" x14ac:dyDescent="0.3">
@@ -27075,7 +27075,7 @@
         <v>977</v>
       </c>
       <c r="E1115" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1116" spans="1:5" x14ac:dyDescent="0.3">
@@ -27092,7 +27092,7 @@
         <v>976</v>
       </c>
       <c r="E1116" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1117" spans="1:5" x14ac:dyDescent="0.3">
@@ -27109,7 +27109,7 @@
         <v>975</v>
       </c>
       <c r="E1117" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1118" spans="1:5" x14ac:dyDescent="0.3">
@@ -27126,7 +27126,7 @@
         <v>974</v>
       </c>
       <c r="E1118" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1119" spans="1:5" x14ac:dyDescent="0.3">
@@ -27143,7 +27143,7 @@
         <v>973</v>
       </c>
       <c r="E1119" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1120" spans="1:5" x14ac:dyDescent="0.3">
@@ -27160,7 +27160,7 @@
         <v>972</v>
       </c>
       <c r="E1120" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1121" spans="1:5" x14ac:dyDescent="0.3">
@@ -27177,7 +27177,7 @@
         <v>971</v>
       </c>
       <c r="E1121" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1122" spans="1:5" x14ac:dyDescent="0.3">
@@ -27194,7 +27194,7 @@
         <v>970</v>
       </c>
       <c r="E1122" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1123" spans="1:5" x14ac:dyDescent="0.3">
@@ -27211,7 +27211,7 @@
         <v>969</v>
       </c>
       <c r="E1123" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1124" spans="1:5" x14ac:dyDescent="0.3">
@@ -27228,7 +27228,7 @@
         <v>968</v>
       </c>
       <c r="E1124" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1125" spans="1:5" x14ac:dyDescent="0.3">
@@ -27245,7 +27245,7 @@
         <v>967</v>
       </c>
       <c r="E1125" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1126" spans="1:5" x14ac:dyDescent="0.3">
@@ -27262,7 +27262,7 @@
         <v>966</v>
       </c>
       <c r="E1126" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1127" spans="1:5" x14ac:dyDescent="0.3">
@@ -27279,7 +27279,7 @@
         <v>965</v>
       </c>
       <c r="E1127" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1128" spans="1:5" x14ac:dyDescent="0.3">
@@ -27296,7 +27296,7 @@
         <v>964</v>
       </c>
       <c r="E1128" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1129" spans="1:5" x14ac:dyDescent="0.3">
@@ -27313,7 +27313,7 @@
         <v>963</v>
       </c>
       <c r="E1129" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1130" spans="1:5" x14ac:dyDescent="0.3">
@@ -27330,7 +27330,7 @@
         <v>962</v>
       </c>
       <c r="E1130" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1131" spans="1:5" x14ac:dyDescent="0.3">
@@ -27347,7 +27347,7 @@
         <v>961</v>
       </c>
       <c r="E1131" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1132" spans="1:5" x14ac:dyDescent="0.3">
@@ -27364,7 +27364,7 @@
         <v>960</v>
       </c>
       <c r="E1132" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1133" spans="1:5" x14ac:dyDescent="0.3">
@@ -27381,7 +27381,7 @@
         <v>959</v>
       </c>
       <c r="E1133" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1134" spans="1:5" x14ac:dyDescent="0.3">
@@ -27398,7 +27398,7 @@
         <v>958</v>
       </c>
       <c r="E1134" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1135" spans="1:5" x14ac:dyDescent="0.3">
@@ -27415,7 +27415,7 @@
         <v>955</v>
       </c>
       <c r="E1135" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1136" spans="1:5" x14ac:dyDescent="0.3">
@@ -27432,7 +27432,7 @@
         <v>954</v>
       </c>
       <c r="E1136" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1137" spans="1:5" x14ac:dyDescent="0.3">
@@ -27449,7 +27449,7 @@
         <v>953</v>
       </c>
       <c r="E1137" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1138" spans="1:5" x14ac:dyDescent="0.3">
@@ -27466,7 +27466,7 @@
         <v>952</v>
       </c>
       <c r="E1138" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1139" spans="1:5" x14ac:dyDescent="0.3">
@@ -27483,7 +27483,7 @@
         <v>951</v>
       </c>
       <c r="E1139" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1140" spans="1:5" x14ac:dyDescent="0.3">
@@ -27500,7 +27500,7 @@
         <v>950</v>
       </c>
       <c r="E1140" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1141" spans="1:5" x14ac:dyDescent="0.3">
@@ -27517,7 +27517,7 @@
         <v>949</v>
       </c>
       <c r="E1141" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1142" spans="1:5" x14ac:dyDescent="0.3">
@@ -27534,7 +27534,7 @@
         <v>948</v>
       </c>
       <c r="E1142" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1143" spans="1:5" x14ac:dyDescent="0.3">
@@ -27551,7 +27551,7 @@
         <v>947</v>
       </c>
       <c r="E1143" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1144" spans="1:5" x14ac:dyDescent="0.3">
@@ -27568,7 +27568,7 @@
         <v>946</v>
       </c>
       <c r="E1144" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1145" spans="1:5" x14ac:dyDescent="0.3">
@@ -27585,7 +27585,7 @@
         <v>945</v>
       </c>
       <c r="E1145" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1146" spans="1:5" x14ac:dyDescent="0.3">
@@ -27602,7 +27602,7 @@
         <v>944</v>
       </c>
       <c r="E1146" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1147" spans="1:5" x14ac:dyDescent="0.3">
@@ -27619,7 +27619,7 @@
         <v>943</v>
       </c>
       <c r="E1147" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1148" spans="1:5" x14ac:dyDescent="0.3">
@@ -27636,7 +27636,7 @@
         <v>942</v>
       </c>
       <c r="E1148" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1149" spans="1:5" x14ac:dyDescent="0.3">
@@ -27653,7 +27653,7 @@
         <v>941</v>
       </c>
       <c r="E1149" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1150" spans="1:5" x14ac:dyDescent="0.3">
@@ -27670,7 +27670,7 @@
         <v>940</v>
       </c>
       <c r="E1150" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1151" spans="1:5" x14ac:dyDescent="0.3">
@@ -27687,7 +27687,7 @@
         <v>939</v>
       </c>
       <c r="E1151" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1152" spans="1:5" x14ac:dyDescent="0.3">
@@ -27704,7 +27704,7 @@
         <v>938</v>
       </c>
       <c r="E1152" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1153" spans="1:5" x14ac:dyDescent="0.3">
@@ -27721,7 +27721,7 @@
         <v>937</v>
       </c>
       <c r="E1153" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1154" spans="1:5" x14ac:dyDescent="0.3">
@@ -27738,7 +27738,7 @@
         <v>936</v>
       </c>
       <c r="E1154" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1155" spans="1:5" x14ac:dyDescent="0.3">
@@ -27755,7 +27755,7 @@
         <v>935</v>
       </c>
       <c r="E1155" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1156" spans="1:5" x14ac:dyDescent="0.3">
@@ -27772,7 +27772,7 @@
         <v>934</v>
       </c>
       <c r="E1156" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1157" spans="1:5" x14ac:dyDescent="0.3">
@@ -27789,7 +27789,7 @@
         <v>933</v>
       </c>
       <c r="E1157" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1158" spans="1:5" x14ac:dyDescent="0.3">
@@ -27806,7 +27806,7 @@
         <v>932</v>
       </c>
       <c r="E1158" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1159" spans="1:5" x14ac:dyDescent="0.3">
@@ -27823,7 +27823,7 @@
         <v>931</v>
       </c>
       <c r="E1159" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1160" spans="1:5" x14ac:dyDescent="0.3">
@@ -27840,7 +27840,7 @@
         <v>930</v>
       </c>
       <c r="E1160" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1161" spans="1:5" x14ac:dyDescent="0.3">
@@ -27857,7 +27857,7 @@
         <v>929</v>
       </c>
       <c r="E1161" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1162" spans="1:5" x14ac:dyDescent="0.3">
@@ -27874,7 +27874,7 @@
         <v>928</v>
       </c>
       <c r="E1162" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1163" spans="1:5" x14ac:dyDescent="0.3">
@@ -27891,7 +27891,7 @@
         <v>927</v>
       </c>
       <c r="E1163" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1164" spans="1:5" x14ac:dyDescent="0.3">
@@ -27908,7 +27908,7 @@
         <v>926</v>
       </c>
       <c r="E1164" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1165" spans="1:5" x14ac:dyDescent="0.3">
@@ -27925,7 +27925,7 @@
         <v>925</v>
       </c>
       <c r="E1165" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1166" spans="1:5" x14ac:dyDescent="0.3">
@@ -27942,7 +27942,7 @@
         <v>924</v>
       </c>
       <c r="E1166" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1167" spans="1:5" x14ac:dyDescent="0.3">
@@ -27959,7 +27959,7 @@
         <v>923</v>
       </c>
       <c r="E1167" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1168" spans="1:5" x14ac:dyDescent="0.3">
@@ -27976,7 +27976,7 @@
         <v>922</v>
       </c>
       <c r="E1168" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1169" spans="1:5" x14ac:dyDescent="0.3">
@@ -27993,7 +27993,7 @@
         <v>921</v>
       </c>
       <c r="E1169" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1170" spans="1:5" x14ac:dyDescent="0.3">
@@ -28010,7 +28010,7 @@
         <v>918</v>
       </c>
       <c r="E1170" t="s">
-        <v>2339</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="1171" spans="1:5" x14ac:dyDescent="0.3">
@@ -28027,7 +28027,7 @@
         <v>917</v>
       </c>
       <c r="E1171" t="s">
-        <v>2339</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="1172" spans="1:5" x14ac:dyDescent="0.3">
@@ -28044,7 +28044,7 @@
         <v>914</v>
       </c>
       <c r="E1172" t="s">
-        <v>2340</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="1173" spans="1:5" x14ac:dyDescent="0.3">
@@ -28061,7 +28061,7 @@
         <v>913</v>
       </c>
       <c r="E1173" t="s">
-        <v>2340</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="1174" spans="1:5" x14ac:dyDescent="0.3">
@@ -28078,7 +28078,7 @@
         <v>912</v>
       </c>
       <c r="E1174" t="s">
-        <v>2340</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="1175" spans="1:5" x14ac:dyDescent="0.3">
@@ -28095,7 +28095,7 @@
         <v>911</v>
       </c>
       <c r="E1175" t="s">
-        <v>2340</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="1176" spans="1:5" x14ac:dyDescent="0.3">
@@ -28112,7 +28112,7 @@
         <v>910</v>
       </c>
       <c r="E1176" t="s">
-        <v>2340</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="1177" spans="1:5" x14ac:dyDescent="0.3">
@@ -28129,7 +28129,7 @@
         <v>909</v>
       </c>
       <c r="E1177" t="s">
-        <v>2340</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="1178" spans="1:5" x14ac:dyDescent="0.3">
@@ -28146,7 +28146,7 @@
         <v>908</v>
       </c>
       <c r="E1178" t="s">
-        <v>2340</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="1179" spans="1:5" x14ac:dyDescent="0.3">
@@ -28163,7 +28163,7 @@
         <v>907</v>
       </c>
       <c r="E1179" t="s">
-        <v>2340</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="1180" spans="1:5" x14ac:dyDescent="0.3">
@@ -28180,7 +28180,7 @@
         <v>904</v>
       </c>
       <c r="E1180" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1181" spans="1:5" x14ac:dyDescent="0.3">
@@ -28197,7 +28197,7 @@
         <v>903</v>
       </c>
       <c r="E1181" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1182" spans="1:5" x14ac:dyDescent="0.3">
@@ -28214,7 +28214,7 @@
         <v>902</v>
       </c>
       <c r="E1182" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1183" spans="1:5" x14ac:dyDescent="0.3">
@@ -28231,7 +28231,7 @@
         <v>901</v>
       </c>
       <c r="E1183" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1184" spans="1:5" x14ac:dyDescent="0.3">
@@ -28248,7 +28248,7 @@
         <v>900</v>
       </c>
       <c r="E1184" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1185" spans="1:5" x14ac:dyDescent="0.3">
@@ -28265,7 +28265,7 @@
         <v>899</v>
       </c>
       <c r="E1185" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1186" spans="1:5" x14ac:dyDescent="0.3">
@@ -28282,7 +28282,7 @@
         <v>898</v>
       </c>
       <c r="E1186" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1187" spans="1:5" x14ac:dyDescent="0.3">
@@ -28299,7 +28299,7 @@
         <v>897</v>
       </c>
       <c r="E1187" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1188" spans="1:5" x14ac:dyDescent="0.3">
@@ -28316,7 +28316,7 @@
         <v>896</v>
       </c>
       <c r="E1188" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1189" spans="1:5" x14ac:dyDescent="0.3">
@@ -28333,7 +28333,7 @@
         <v>895</v>
       </c>
       <c r="E1189" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1190" spans="1:5" x14ac:dyDescent="0.3">
@@ -28350,7 +28350,7 @@
         <v>894</v>
       </c>
       <c r="E1190" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1191" spans="1:5" x14ac:dyDescent="0.3">
@@ -28367,7 +28367,7 @@
         <v>893</v>
       </c>
       <c r="E1191" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1192" spans="1:5" x14ac:dyDescent="0.3">
@@ -28384,7 +28384,7 @@
         <v>892</v>
       </c>
       <c r="E1192" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1193" spans="1:5" x14ac:dyDescent="0.3">
@@ -28401,7 +28401,7 @@
         <v>891</v>
       </c>
       <c r="E1193" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1194" spans="1:5" x14ac:dyDescent="0.3">
@@ -28418,7 +28418,7 @@
         <v>890</v>
       </c>
       <c r="E1194" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1195" spans="1:5" x14ac:dyDescent="0.3">
@@ -28435,7 +28435,7 @@
         <v>889</v>
       </c>
       <c r="E1195" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1196" spans="1:5" x14ac:dyDescent="0.3">
@@ -28452,7 +28452,7 @@
         <v>888</v>
       </c>
       <c r="E1196" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1197" spans="1:5" x14ac:dyDescent="0.3">
@@ -28469,7 +28469,7 @@
         <v>887</v>
       </c>
       <c r="E1197" t="s">
-        <v>2341</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="1198" spans="1:5" x14ac:dyDescent="0.3">
@@ -28486,7 +28486,7 @@
         <v>884</v>
       </c>
       <c r="E1198" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1199" spans="1:5" x14ac:dyDescent="0.3">
@@ -28503,7 +28503,7 @@
         <v>883</v>
       </c>
       <c r="E1199" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1200" spans="1:5" x14ac:dyDescent="0.3">
@@ -28520,7 +28520,7 @@
         <v>882</v>
       </c>
       <c r="E1200" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1201" spans="1:5" x14ac:dyDescent="0.3">
@@ -28537,7 +28537,7 @@
         <v>881</v>
       </c>
       <c r="E1201" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1202" spans="1:5" x14ac:dyDescent="0.3">
@@ -28554,7 +28554,7 @@
         <v>880</v>
       </c>
       <c r="E1202" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1203" spans="1:5" x14ac:dyDescent="0.3">
@@ -28571,7 +28571,7 @@
         <v>879</v>
       </c>
       <c r="E1203" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1204" spans="1:5" x14ac:dyDescent="0.3">
@@ -28588,7 +28588,7 @@
         <v>878</v>
       </c>
       <c r="E1204" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1205" spans="1:5" x14ac:dyDescent="0.3">
@@ -28605,7 +28605,7 @@
         <v>877</v>
       </c>
       <c r="E1205" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1206" spans="1:5" x14ac:dyDescent="0.3">
@@ -28622,7 +28622,7 @@
         <v>876</v>
       </c>
       <c r="E1206" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1207" spans="1:5" x14ac:dyDescent="0.3">
@@ -28639,7 +28639,7 @@
         <v>875</v>
       </c>
       <c r="E1207" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1208" spans="1:5" x14ac:dyDescent="0.3">
@@ -28656,7 +28656,7 @@
         <v>874</v>
       </c>
       <c r="E1208" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1209" spans="1:5" x14ac:dyDescent="0.3">
@@ -28673,7 +28673,7 @@
         <v>873</v>
       </c>
       <c r="E1209" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1210" spans="1:5" x14ac:dyDescent="0.3">
@@ -28690,7 +28690,7 @@
         <v>872</v>
       </c>
       <c r="E1210" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1211" spans="1:5" x14ac:dyDescent="0.3">
@@ -28707,7 +28707,7 @@
         <v>871</v>
       </c>
       <c r="E1211" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1212" spans="1:5" x14ac:dyDescent="0.3">
@@ -28724,7 +28724,7 @@
         <v>870</v>
       </c>
       <c r="E1212" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1213" spans="1:5" x14ac:dyDescent="0.3">
@@ -28741,7 +28741,7 @@
         <v>869</v>
       </c>
       <c r="E1213" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1214" spans="1:5" x14ac:dyDescent="0.3">
@@ -28758,7 +28758,7 @@
         <v>868</v>
       </c>
       <c r="E1214" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1215" spans="1:5" x14ac:dyDescent="0.3">
@@ -28775,7 +28775,7 @@
         <v>867</v>
       </c>
       <c r="E1215" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1216" spans="1:5" x14ac:dyDescent="0.3">
@@ -28792,7 +28792,7 @@
         <v>866</v>
       </c>
       <c r="E1216" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1217" spans="1:5" x14ac:dyDescent="0.3">
@@ -28809,7 +28809,7 @@
         <v>865</v>
       </c>
       <c r="E1217" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1218" spans="1:5" x14ac:dyDescent="0.3">
@@ -28826,7 +28826,7 @@
         <v>864</v>
       </c>
       <c r="E1218" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1219" spans="1:5" x14ac:dyDescent="0.3">
@@ -28843,7 +28843,7 @@
         <v>863</v>
       </c>
       <c r="E1219" t="s">
-        <v>2342</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1220" spans="1:5" x14ac:dyDescent="0.3">
@@ -28860,7 +28860,7 @@
         <v>860</v>
       </c>
       <c r="E1220" t="s">
-        <v>2343</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="1221" spans="1:5" x14ac:dyDescent="0.3">
@@ -28877,7 +28877,7 @@
         <v>859</v>
       </c>
       <c r="E1221" t="s">
-        <v>2344</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="1222" spans="1:5" x14ac:dyDescent="0.3">
@@ -28894,7 +28894,7 @@
         <v>858</v>
       </c>
       <c r="E1222" t="s">
-        <v>2345</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="1223" spans="1:5" x14ac:dyDescent="0.3">
@@ -28911,7 +28911,7 @@
         <v>857</v>
       </c>
       <c r="E1223" t="s">
-        <v>2346</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="1224" spans="1:5" x14ac:dyDescent="0.3">
@@ -28928,7 +28928,7 @@
         <v>856</v>
       </c>
       <c r="E1224" t="s">
-        <v>2347</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="1225" spans="1:5" x14ac:dyDescent="0.3">
@@ -28945,7 +28945,7 @@
         <v>855</v>
       </c>
       <c r="E1225" t="s">
-        <v>2348</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="1226" spans="1:5" x14ac:dyDescent="0.3">
@@ -28962,7 +28962,7 @@
         <v>854</v>
       </c>
       <c r="E1226" t="s">
-        <v>2349</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="1227" spans="1:5" x14ac:dyDescent="0.3">
@@ -28979,7 +28979,7 @@
         <v>853</v>
       </c>
       <c r="E1227" t="s">
-        <v>2350</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="1228" spans="1:5" x14ac:dyDescent="0.3">
@@ -28996,7 +28996,7 @@
         <v>852</v>
       </c>
       <c r="E1228" t="s">
-        <v>2351</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="1229" spans="1:5" x14ac:dyDescent="0.3">
@@ -29013,7 +29013,7 @@
         <v>851</v>
       </c>
       <c r="E1229" t="s">
-        <v>2352</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="1230" spans="1:5" x14ac:dyDescent="0.3">
@@ -29030,7 +29030,7 @@
         <v>850</v>
       </c>
       <c r="E1230" t="s">
-        <v>2353</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="1231" spans="1:5" x14ac:dyDescent="0.3">
